--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{429B5309-1B10-47C6-94C9-9BFDC964468D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB6A9A4-A1CE-4A33-8D36-90F0687E7B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-86" yWindow="0" windowWidth="11143" windowHeight="11709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2571" yWindow="2571" windowWidth="16458" windowHeight="8426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="36">
   <si>
     <t>понедельник</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>11-Б</t>
+  </si>
+  <si>
+    <t>Учитель</t>
   </si>
 </sst>
 </file>
@@ -175,7 +178,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -198,25 +201,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -499,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.84375" customWidth="1"/>
@@ -507,21 +514,24 @@
     <col min="4" max="4" width="12.15234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -535,8 +545,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
         <v>34</v>
       </c>
       <c r="B3" t="s">
@@ -549,8 +559,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
         <v>34</v>
       </c>
       <c r="B4" t="s">
@@ -563,8 +573,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
       <c r="B5" t="s">
@@ -577,8 +587,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
         <v>34</v>
       </c>
       <c r="B6" t="s">
@@ -591,8 +601,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
         <v>34</v>
       </c>
       <c r="B7" t="s">
@@ -605,8 +615,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
         <v>34</v>
       </c>
       <c r="B8" t="s">
@@ -619,8 +629,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
         <v>34</v>
       </c>
       <c r="B9" t="s">
@@ -633,8 +643,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -647,8 +657,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
         <v>34</v>
       </c>
       <c r="B11" t="s">
@@ -661,8 +671,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
         <v>34</v>
       </c>
       <c r="B12" t="s">
@@ -675,8 +685,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
         <v>34</v>
       </c>
       <c r="B13" t="s">
@@ -689,8 +699,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
         <v>34</v>
       </c>
       <c r="B14" t="s">
@@ -703,8 +713,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
         <v>34</v>
       </c>
       <c r="B15" t="s">
@@ -717,8 +727,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
         <v>34</v>
       </c>
       <c r="B16" t="s">
@@ -732,7 +742,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A17" s="6" t="s">
+      <c r="A17" t="s">
         <v>34</v>
       </c>
       <c r="B17" t="s">
@@ -746,7 +756,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A18" s="6" t="s">
+      <c r="A18" t="s">
         <v>34</v>
       </c>
       <c r="B18" t="s">
@@ -760,7 +770,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A19" s="6" t="s">
+      <c r="A19" t="s">
         <v>34</v>
       </c>
       <c r="B19" t="s">
@@ -774,7 +784,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A20" s="6" t="s">
+      <c r="A20" t="s">
         <v>34</v>
       </c>
       <c r="B20" t="s">
@@ -788,7 +798,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
+      <c r="A21" t="s">
         <v>34</v>
       </c>
       <c r="B21" t="s">
@@ -802,7 +812,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A22" s="6" t="s">
+      <c r="A22" t="s">
         <v>34</v>
       </c>
       <c r="B22" t="s">
@@ -816,7 +826,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
+      <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" t="s">
@@ -830,7 +840,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
+      <c r="A24" t="s">
         <v>34</v>
       </c>
       <c r="B24" t="s">
@@ -844,7 +854,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A25" s="6" t="s">
+      <c r="A25" t="s">
         <v>34</v>
       </c>
       <c r="B25" t="s">
@@ -858,7 +868,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A26" s="6" t="s">
+      <c r="A26" t="s">
         <v>34</v>
       </c>
       <c r="B26" t="s">
@@ -872,7 +882,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A27" s="6" t="s">
+      <c r="A27" t="s">
         <v>34</v>
       </c>
       <c r="B27" t="s">
@@ -886,7 +896,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A28" s="6" t="s">
+      <c r="A28" t="s">
         <v>34</v>
       </c>
       <c r="B28" t="s">
@@ -900,7 +910,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A29" s="6" t="s">
+      <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="B29" t="s">
@@ -914,7 +924,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A30" s="6" t="s">
+      <c r="A30" t="s">
         <v>34</v>
       </c>
       <c r="B30" t="s">
@@ -928,7 +938,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A31" s="6" t="s">
+      <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31" t="s">
@@ -942,7 +952,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A32" s="6" t="s">
+      <c r="A32" t="s">
         <v>34</v>
       </c>
       <c r="B32" t="s">

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB6A9A4-A1CE-4A33-8D36-90F0687E7B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECE0719-2498-41FD-B7A9-8E1D82B18119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2571" yWindow="2571" windowWidth="16458" windowHeight="8426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2914" yWindow="2914" windowWidth="16457" windowHeight="8426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
